--- a/SPECIAL EVENTS EXPENSES/New Year Expenses.xlsx
+++ b/SPECIAL EVENTS EXPENSES/New Year Expenses.xlsx
@@ -27,7 +27,58 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_E589E6B1C21148AE99526AF67611A84C" descr="WhatsApp Image 2025-11-22 at 17.08.02_02bf6d70"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5759450" y="541020"/>
+          <a:ext cx="2849245" cy="5125720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_4670CFCA6631443A8C592991E285D7D6" descr="WhatsApp Image 2025-11-21 at 17.16.31_bae62e2c"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5596890" y="300355"/>
+          <a:ext cx="2766060" cy="4973955"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,7 +787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -822,12 +873,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1387,7 +1432,7 @@
     <col min="4" max="4" width="7.21904761904762" style="5" customWidth="1"/>
     <col min="5" max="5" width="39.3142857142857" style="3" customWidth="1"/>
     <col min="6" max="6" width="22.1904761904762" style="6" customWidth="1"/>
-    <col min="7" max="8" width="17.7142857142857" style="7" customWidth="1"/>
+    <col min="7" max="8" width="20.8571428571429" style="7" customWidth="1"/>
     <col min="9" max="9" width="25.4285714285714" style="8" customWidth="1"/>
     <col min="10" max="16384" width="9.14285714285714" style="9"/>
   </cols>
@@ -1417,12 +1462,14 @@
       <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="16"/>
+    <row r="2" ht="369.35" spans="1:12">
+      <c r="A2" s="16">
+        <v>45982</v>
+      </c>
       <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
@@ -1432,19 +1479,30 @@
       <c r="D2" s="19">
         <v>1</v>
       </c>
-      <c r="E2" s="20"/>
+      <c r="E2" s="20" t="str">
+        <f>_xlfn.DISPIMG("ID_4670CFCA6631443A8C592991E285D7D6",1)</f>
+        <v>=DISPIMG("ID_4670CFCA6631443A8C592991E285D7D6",1)</v>
+      </c>
       <c r="F2" s="21">
         <v>4000000</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="32" t="s">
+      <c r="G2" s="22">
+        <f>SUM(F2)</f>
+        <v>4000000</v>
+      </c>
+      <c r="H2" s="22">
+        <f>SUM(G2)</f>
+        <v>4000000</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="33"/>
+      <c r="L2" s="31"/>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="16"/>
+    <row r="3" ht="369.5" spans="1:11">
+      <c r="A3" s="16">
+        <v>45983</v>
+      </c>
       <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
@@ -1454,16 +1512,25 @@
       <c r="D3" s="24">
         <v>1</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="20" t="str">
+        <f>_xlfn.DISPIMG("ID_E589E6B1C21148AE99526AF67611A84C",1)</f>
+        <v>=DISPIMG("ID_E589E6B1C21148AE99526AF67611A84C",1)</v>
+      </c>
       <c r="F3" s="21">
         <v>7500000</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="32" t="s">
+      <c r="G3" s="22">
+        <f>SUM(F3)</f>
+        <v>7500000</v>
+      </c>
+      <c r="H3" s="22">
+        <f>SUM(G3)</f>
+        <v>7500000</v>
+      </c>
+      <c r="I3" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="33"/>
+      <c r="K3" s="31"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="16"/>
@@ -1474,8 +1541,8 @@
       <c r="F4" s="21"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
-      <c r="I4" s="32"/>
-      <c r="K4" s="33"/>
+      <c r="I4" s="30"/>
+      <c r="K4" s="31"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="16"/>
@@ -1486,7 +1553,7 @@
       <c r="F5" s="21"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
-      <c r="I5" s="32"/>
+      <c r="I5" s="30"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="16"/>
@@ -1497,7 +1564,7 @@
       <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
-      <c r="I6" s="32"/>
+      <c r="I6" s="30"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="16"/>
@@ -1508,7 +1575,7 @@
       <c r="F7" s="21"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
-      <c r="I7" s="32"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="16"/>
@@ -1519,7 +1586,7 @@
       <c r="F8" s="21"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
-      <c r="I8" s="32"/>
+      <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="16"/>
@@ -1530,8 +1597,8 @@
       <c r="F9" s="21"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
-      <c r="I9" s="32"/>
-      <c r="K9" s="33"/>
+      <c r="I9" s="30"/>
+      <c r="K9" s="31"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="16"/>
@@ -1542,8 +1609,8 @@
       <c r="F10" s="21"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
-      <c r="I10" s="32"/>
-      <c r="K10" s="33"/>
+      <c r="I10" s="30"/>
+      <c r="K10" s="31"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="16"/>
@@ -1554,8 +1621,8 @@
       <c r="F11" s="21"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="32"/>
-      <c r="K11" s="33"/>
+      <c r="I11" s="30"/>
+      <c r="K11" s="31"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="16"/>
@@ -1566,22 +1633,22 @@
       <c r="F12" s="21"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
-      <c r="I12" s="32"/>
-      <c r="K12" s="33"/>
+      <c r="I12" s="30"/>
+      <c r="K12" s="31"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
-      <c r="E13" s="29">
+      <c r="E13" s="26">
         <f>SUM(H2:H11)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="32"/>
+        <v>11500000</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
